--- a/out/Attention_Base_repeat_1_000008.xlsx
+++ b/out/Attention_Base_repeat_1_000008.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>0.5195375025212519</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.315708769287449e-05</v>
+        <v>-9.816461868956685e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1070196012911481</v>
+        <v>-0.1127722926212568</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1128704572399463</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.107195290178011</v>
+        <v>-0.1129573696428267</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2967655539730406</v>
+        <v>0.3125169505282293</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4869056184988809</v>
+        <v>0.5126770898815103</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0211444468266281</v>
+        <v>0.02226676711035193</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2319529869918532</v>
+        <v>0.2441919211011112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03708028369412986</v>
+        <v>0.03904845107356484</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2849619779636297</v>
+        <v>0.3000145520036933</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04504816554161525</v>
+        <v>0.04743894468237206</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3379744971440681</v>
+        <v>0.3558408989627548</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0119208732929875</v>
+        <v>0.01255353335507484</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3167105636086252</v>
+        <v>0.333448160030849</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00662071862793783</v>
+        <v>0.006972549423297319</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3180218968864733</v>
+        <v>0.3348293896747909</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01391396089809551</v>
+        <v>0.01465383921826005</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3392374891218566</v>
+        <v>0.3571717483522512</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005462997413779955</v>
+        <v>0.005753655083615435</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.336238264329596</v>
+        <v>0.3540137104263394</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003889903535221407</v>
+        <v>0.004095170816307035</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3385515840686287</v>
+        <v>0.3564497235853313</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001528059163496676</v>
+        <v>0.001609532635427412</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.337714767537842</v>
+        <v>0.3555687006844412</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008643570261933406</v>
+        <v>0.0009105994212036247</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3379160715260736</v>
+        <v>0.3557809685155333</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003261721230522456</v>
+        <v>0.0003437876615124714</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3377029962801158</v>
+        <v>0.3555568449844136</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001502354225216803</v>
+        <v>0.0001590431060690097</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3376769859358545</v>
+        <v>0.3555297202309075</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.232009589913218e-05</v>
+        <v>5.47420717821941e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3376301586008151</v>
+        <v>0.3554808315557488</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>1.264847281138308e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3376016502520689</v>
+        <v>0.3554509987720127</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3375966368485123</v>
+        <v>0.355445984623814</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.337592291222703</v>
+        <v>0.3554416757464965</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3375889408679101</v>
+        <v>0.3554385081249317</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3375835715409224</v>
+        <v>0.355433138797944</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3375775788074921</v>
+        <v>0.3554271460645136</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3375722110189137</v>
+        <v>0.3554217782759352</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3375722477674054</v>
+        <v>0.3554218150244269</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3375723580128809</v>
+        <v>0.3554219252699025</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3375724315098645</v>
+        <v>0.3554219987668861</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3375726152523237</v>
+        <v>0.3554221825093452</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3375741586889802</v>
+        <v>0.3554237259460017</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3375756286286533</v>
+        <v>0.3554251958856748</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3375768780773752</v>
+        <v>0.3554264453343968</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3375782377715725</v>
+        <v>0.3554278050285941</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3375760328620633</v>
+        <v>0.3554256001190848</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3375756286286533</v>
+        <v>0.3554251958856748</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.3554243506703628</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3375753346407185</v>
+        <v>0.3554249018977401</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3375750039042921</v>
+        <v>0.3554245711613137</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3375747099163576</v>
+        <v>0.3554242771733792</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.3554243506703628</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3375743424314393</v>
+        <v>0.3554239096884609</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3375742321859638</v>
+        <v>0.3554237994429854</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3375741954374721</v>
+        <v>0.3554237626944937</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3375743424314393</v>
+        <v>0.3554239096884609</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3375738647010457</v>
+        <v>0.3554234319580672</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.337574820161833</v>
+        <v>0.3554243874188545</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.3554243506703628</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3375744526769149</v>
+        <v>0.3554240199339364</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3375748936588168</v>
+        <v>0.3554244609158383</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3375742689344557</v>
+        <v>0.3554238361914773</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3375740851919966</v>
+        <v>0.3554236524490181</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3375736809585865</v>
+        <v>0.3554232482156081</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3375728357432745</v>
+        <v>0.3554224030002961</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3375727989947828</v>
+        <v>0.3554223662518044</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3375729459887501</v>
+        <v>0.3554225132457716</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3375728724917665</v>
+        <v>0.355422439748788</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3375729459887501</v>
+        <v>0.3554225132457716</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.337572982737242</v>
+        <v>0.3554225499942636</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3375728724917665</v>
+        <v>0.355422439748788</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3375733134736684</v>
+        <v>0.3554228807306899</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3375732032281928</v>
+        <v>0.3554227704852144</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3375731664797009</v>
+        <v>0.3554227337367225</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3375730929827173</v>
+        <v>0.3554226602397389</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3375730562342256</v>
+        <v>0.3554226234912472</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3375728357432745</v>
+        <v>0.3554224030002961</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3375727622462909</v>
+        <v>0.3554223295033125</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-9.227858435864233</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3375726887493073</v>
+        <v>0.3554222560063289</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-9.227858435864233</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3375727254977992</v>
+        <v>0.3554222927548208</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-9.227858435864233</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3375726152523237</v>
+        <v>0.3554221825093452</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3375727254977992</v>
+        <v>0.3554222927548208</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.08046249747874815</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3375730194857337</v>
+        <v>0.3554225867427552</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_1_000008.xlsx
+++ b/out/Attention_Base_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.315708769287449e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1070196012911481</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.107195290178011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2967655539730406</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4869056184988809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0211444468266281</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2319529869918532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03708028369412986</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2849619779636297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04504816554161525</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3379744971440681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0119208732929875</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3167105636086252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00662071862793783</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3180218968864733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01391396089809551</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3392374891218566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005462997413779955</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.336238264329596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003889903535221407</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3385515840686287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001528059163496676</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.337714767537842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008643570261933406</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3379160715260736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003261721230522456</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3377029962801158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001502354225216803</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3376769859358545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.232009589913218e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3376301586008151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3376016502520689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3375966368485123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.337592291222703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3375889408679101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3375835715409224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3375775788074921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3375722110189137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3375722477674054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3375723580128809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3375724315098645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3375726152523237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3375741586889802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3375756286286533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3375768780773752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3375782377715725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3375760328620633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3375756286286533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3375753346407185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3375750039042921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3375747099163576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3375743424314393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3375742321859638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3375741954374721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3375743424314393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3375738647010457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.337574820161833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3375744526769149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3375748936588168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3375742689344557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3375740851919966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3375736809585865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3375728357432745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3375727989947828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3375729459887501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3375728724917665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3375729459887501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.337572982737242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3375728724917665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3375733134736684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3375732032281928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3375731664797009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3375730929827173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3375730562342256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3375728357432745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3375727622462909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3375726887493073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3375727254977992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3375726152523237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3375727254977992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.082561524747701e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3375730194857337</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_1_000008.xlsx
+++ b/out/Attention_Base_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006945758126676083</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.009239403530955315</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.01369290519505739</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.02396920695900917</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.02754620090126991</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.02539387717843056</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.02280045300722122</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.02131780609488487</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01912852562963963</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01769842952489853</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01623886451125145</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.01532250922173262</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01423856057226658</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01342261955142021</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01291632279753685</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.01308522000908852</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01230546180158854</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01157508511096239</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01092598866671324</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01027141604572535</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.009714331477880478</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.008979661390185356</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008479403331875801</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.008044082671403885</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.00796870794147253</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.007456105202436447</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.007101829163730145</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.006590620614588261</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.006210809573531151</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.006103319115936756</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.006320187821984291</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.007024895399808884</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.00691293366253376</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.006843998096883297</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.006917700171470642</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.006731631234288216</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.006695634685456753</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.006460802629590034</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.00642591156065464</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.006516286171972752</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.006584213115274906</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.006870737299323082</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.007426264695823193</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.008688514120876789</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-8.677021837199572e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.0996823151528278</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.009713172912597656</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.009735079482197762</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01018644310534</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01014750078320503</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01022564712911844</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01004173513501883</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01001832820475101</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.009943371638655663</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01006633136421442</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01008558832108974</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01014651078730822</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01016505341976881</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01023947633802891</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01058858446776867</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>-0.09983640019362326</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.2420487711163884</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01124460529536009</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.3847258845432196</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.01724588753620422</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01122343167662621</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.1767806890374937</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.03024341070049998</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01159668248146772</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.220016051291608</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.03674217228264796</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01218609884381294</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.2632544749647521</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.009722084666365155</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0121442973613739</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.2459100827032754</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.005399399839875535</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01251556631177664</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.2469787462787987</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>0.01134750797502474</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01387539692223072</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.2642817883356363</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>0.004455384158350294</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01452333386987448</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.261834593029404</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>0.003170605583854123</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01525950990617275</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.2637202875966686</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>0.001245617794136793</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01530789956450462</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.2630367198155753</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>0.0007040500568243558</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01568546891212463</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.2632000158152247</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>0.000265104923056796</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01558435522019863</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.2630252412911607</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>0.0001216104509928598</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01552722509950399</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.263003091642142</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01530786231160164</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.2629639228332366</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01507201511412859</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.2629397185258858</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01505302079021931</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.2629347081008973</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01509850658476353</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.262930253807093</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01515535078942776</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.2629267197098411</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01505240611732006</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.2629214238798369</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01479382999241352</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.2629157618828332</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01463652960956097</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.262915578140374</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01462044939398766</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.2629156148888657</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01468668133020401</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.2629157251343413</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01467176526784897</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.2629157986313249</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01478111930191517</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.2629159823737841</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01576261408627033</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.2629175258104405</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01691544055938721</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.2629189957501136</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01768537051975727</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.2629202451988356</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.03987820446491241</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.2629216048930329</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.07100679725408554</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.2629193999835236</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.04507550969719887</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.2629189957501136</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.04603169113397598</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.2629181505348017</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.06050360947847366</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.2629187017621789</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.05798735469579697</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.2629183710257525</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.05233728140592575</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.2629180770378181</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.04873726144433022</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.2629181505348017</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.04596865549683571</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.2629177095528997</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.04387331381440163</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.2629175993074241</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.04377593100070953</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.2629175625589324</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.04024931788444519</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.2629177095528997</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0317922979593277</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.262917231822506</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.03818284720182419</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.2629181872832934</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.04815061017870903</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.2629181505348017</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.04751723632216454</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.2629178197983753</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.05110189691185951</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.2629182607802772</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.04173049330711365</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.2629176360559161</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.03752313926815987</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.2629174523134569</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.03170386701822281</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.2629170480800469</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02760046534240246</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.2629162028647349</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02760610915720463</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.2629161661162432</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02758343890309334</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.2629163131102105</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0283355712890625</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.2629162396132269</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02718620933592319</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.2629163131102105</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02871121093630791</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.2629163498587024</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02790304832160473</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.2629162396132269</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.03143046051263809</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.2629166805951288</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0305955708026886</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.2629165703496533</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.03075739555060863</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.2629165336011614</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02935080230236053</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.2629164601041777</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02873879298567772</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.262916423355686</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02734500356018543</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.2629162028647349</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02651755698025227</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.2629161293677513</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02605566941201687</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.2629160558707677</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.02604344487190247</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.2629160926192596</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.02525573782622814</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.2629159823737841</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.02565202862024307</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999995</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.2629160926192596</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.082561524747701e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.02714604511857033</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.2629163866071941</v>
       </c>
     </row>
   </sheetData>
